--- a/VerveStacks_UGA_grids_kan/vt_vervestacks_UGA_v1.xlsx
+++ b/VerveStacks_UGA_grids_kan/vt_vervestacks_UGA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_UGA_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{545CA0C0-71DB-4CA1-9A60-8C6E2A5B0451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{38C724DE-9EA3-4439-998E-48DFEA304D04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{86793527-B6B5-4976-BC65-706E71ED808E}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{FA61393A-4324-46BD-9D7C-CA3FBFE3DC82}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -778,7 +778,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0128DEA-90BB-4ED0-BB06-D5993089B418}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7DADC41-18E6-4970-B70E-8A1E2B44754C}">
   <dimension ref="B9:T13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1020,7 +1020,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC2ED1B3-4A32-4DED-953B-CE021B2E562B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C67139DB-4377-4E0F-91AA-6FB32DC5F5AB}">
   <dimension ref="B9:T26"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1954,7 +1954,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3593665F-03D6-4B78-B1D9-DB09F8E2D94C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6982988-5AE4-4C6A-A6BF-824BFE85A295}">
   <dimension ref="B9:T36"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3316,7 +3316,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45F0A8ED-D814-443F-B854-BC4D449A54E7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37EB7AF2-9485-4937-97B8-977A4A7B0BAF}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
